--- a/Thông số kỹ thuật của Server Đông Á.xlsx
+++ b/Thông số kỹ thuật của Server Đông Á.xlsx
@@ -9,11 +9,12 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" activeTab="1"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="47">
   <si>
     <t xml:space="preserve">Tên sản phẩm </t>
   </si>
@@ -460,12 +461,24 @@
   <si>
     <t xml:space="preserve">Tản Viên </t>
   </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -549,8 +562,23 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -563,8 +591,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -711,11 +744,225 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top style="dotted">
+        <color indexed="64"/>
+      </top>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="dotted">
+        <color indexed="64"/>
+      </top>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top style="dotted">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="dotted">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top style="dotted">
+        <color indexed="64"/>
+      </top>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top style="dotted">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="dotted">
+        <color indexed="64"/>
+      </top>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="dotted">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -775,71 +1022,114 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1152,6 +1442,87 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="C3:J6"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="9.140625" style="42"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" customWidth="1"/>
+    <col min="8" max="8" width="18.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="49"/>
+      <c r="D3" s="50">
+        <v>2</v>
+      </c>
+      <c r="E3" s="50">
+        <v>3</v>
+      </c>
+      <c r="F3" s="50">
+        <v>4</v>
+      </c>
+      <c r="G3" s="50">
+        <v>5</v>
+      </c>
+      <c r="H3" s="50">
+        <v>6</v>
+      </c>
+      <c r="I3" s="50">
+        <v>7</v>
+      </c>
+      <c r="J3" s="51" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="3:10" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="52"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="48"/>
+    </row>
+    <row r="5" spans="3:10" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="53"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="44"/>
+    </row>
+    <row r="6" spans="3:10" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C6" s="57" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="54"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:C6"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1200,7 +1571,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1231,7 +1602,7 @@
       <c r="A2" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="21" t="s">
         <v>21</v>
       </c>
       <c r="C2" s="10" t="s">
@@ -1246,7 +1617,7 @@
     </row>
     <row r="3" spans="1:5" ht="87" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="20"/>
-      <c r="B3" s="41"/>
+      <c r="B3" s="21"/>
       <c r="C3" s="11" t="s">
         <v>16</v>
       </c>
@@ -1259,7 +1630,7 @@
     </row>
     <row r="4" spans="1:5" ht="87" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20"/>
-      <c r="B4" s="41"/>
+      <c r="B4" s="21"/>
       <c r="C4" s="12" t="s">
         <v>17</v>
       </c>
@@ -1274,83 +1645,83 @@
       <c r="A5" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="35" t="s">
+      <c r="C5" s="23"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="29" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="20"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="36"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="30"/>
     </row>
     <row r="7" spans="1:5" ht="236.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="20"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="37"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="31"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="29"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="35" t="s">
+      <c r="C8" s="23"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="29" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="20"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="36"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="30"/>
     </row>
     <row r="10" spans="1:5" ht="261.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="20"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="37"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="31"/>
     </row>
     <row r="11" spans="1:5" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="39" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="20"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="28"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="40"/>
     </row>
     <row r="13" spans="1:5" ht="134.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="20"/>
-      <c r="B13" s="21"/>
+      <c r="B13" s="22"/>
       <c r="C13" s="13" t="s">
         <v>16</v>
       </c>
@@ -1365,56 +1736,56 @@
       <c r="A14" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="29"/>
+      <c r="C14" s="23"/>
       <c r="D14" s="32"/>
-      <c r="E14" s="35" t="s">
+      <c r="E14" s="29" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="20"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="30"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="24"/>
       <c r="D15" s="33"/>
-      <c r="E15" s="36"/>
+      <c r="E15" s="30"/>
     </row>
     <row r="16" spans="1:5" ht="288.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="20"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="31"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="25"/>
       <c r="D16" s="34"/>
-      <c r="E16" s="37"/>
+      <c r="E16" s="31"/>
     </row>
     <row r="17" spans="1:5" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="24" t="s">
+      <c r="D17" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="E17" s="26" t="s">
+      <c r="E17" s="39" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="20"/>
-      <c r="B18" s="21"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="27"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="41"/>
     </row>
     <row r="19" spans="1:5" ht="138.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="20"/>
-      <c r="B19" s="21"/>
+      <c r="B19" s="22"/>
       <c r="C19" s="13" t="s">
         <v>16</v>
       </c>
@@ -1427,11 +1798,21 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E14:E16"/>
     <mergeCell ref="D5:D7"/>
     <mergeCell ref="E5:E7"/>
     <mergeCell ref="A8:A10"/>
@@ -1439,21 +1820,11 @@
     <mergeCell ref="C8:C10"/>
     <mergeCell ref="D8:D10"/>
     <mergeCell ref="E8:E10"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Thông số kỹ thuật của Server Đông Á.xlsx
+++ b/Thông số kỹ thuật của Server Đông Á.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Realstate\AAADongA_skill\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AAADongA_skill\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{261C1443-8743-45B8-85A5-8D5678B978AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
@@ -21,21 +22,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="48">
   <si>
     <t xml:space="preserve">Tên sản phẩm </t>
   </si>
@@ -473,11 +465,14 @@
   <si>
     <t>T</t>
   </si>
+  <si>
+    <t>ML</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1001,13 +996,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1018,72 +1013,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1126,6 +1055,72 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1441,79 +1436,83 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="C3:J6"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="9.140625" style="42"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" customWidth="1"/>
-    <col min="8" max="8" width="18.28515625" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" style="20"/>
+    <col min="4" max="4" width="15.5546875" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" customWidth="1"/>
+    <col min="7" max="7" width="15.5546875" customWidth="1"/>
+    <col min="8" max="8" width="18.33203125" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" customWidth="1"/>
+    <col min="10" max="10" width="15.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="49"/>
-      <c r="D3" s="50">
+    <row r="3" spans="3:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="27"/>
+      <c r="D3" s="28">
         <v>2</v>
       </c>
-      <c r="E3" s="50">
+      <c r="E3" s="28">
         <v>3</v>
       </c>
-      <c r="F3" s="50">
+      <c r="F3" s="28">
         <v>4</v>
       </c>
-      <c r="G3" s="50">
+      <c r="G3" s="28">
         <v>5</v>
       </c>
-      <c r="H3" s="50">
+      <c r="H3" s="28">
         <v>6</v>
       </c>
-      <c r="I3" s="50">
+      <c r="I3" s="28">
         <v>7</v>
       </c>
-      <c r="J3" s="51" t="s">
+      <c r="J3" s="29" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="3:10" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="55" t="s">
+    <row r="4" spans="3:10" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C4" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="D4" s="52"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="48"/>
-    </row>
-    <row r="5" spans="3:10" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="56" t="s">
+      <c r="D4" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="26"/>
+    </row>
+    <row r="5" spans="3:10" ht="52.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C5" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="53"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="44"/>
-    </row>
-    <row r="6" spans="3:10" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="57" t="s">
+      <c r="D5" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="22"/>
+    </row>
+    <row r="6" spans="3:10" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C6" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="54"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="46"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1522,18 +1521,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B3:C6"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="1"/>
-    <col min="2" max="2" width="23.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="96.140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="17.7109375" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.85546875" style="1"/>
+    <col min="1" max="1" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="23.88671875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="96.109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:3" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:3" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
@@ -1541,7 +1540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:3" ht="341.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:3" ht="341.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
@@ -1549,7 +1548,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="2:3" ht="345.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:3" ht="345.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>3</v>
       </c>
@@ -1557,7 +1556,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:3" ht="300.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:3" ht="300.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>4</v>
       </c>
@@ -1572,18 +1571,18 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" customWidth="1"/>
-    <col min="2" max="2" width="79.85546875" customWidth="1"/>
-    <col min="3" max="3" width="5.85546875" style="8" customWidth="1"/>
-    <col min="4" max="4" width="68.42578125" customWidth="1"/>
-    <col min="5" max="5" width="62.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.33203125" customWidth="1"/>
+    <col min="2" max="2" width="79.88671875" customWidth="1"/>
+    <col min="3" max="3" width="5.88671875" style="8" customWidth="1"/>
+    <col min="4" max="4" width="68.44140625" customWidth="1"/>
+    <col min="5" max="5" width="62.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>13</v>
       </c>
@@ -1598,11 +1597,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="87" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+    <row r="2" spans="1:5" ht="87" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="57" t="s">
         <v>21</v>
       </c>
       <c r="C2" s="10" t="s">
@@ -1615,9 +1614,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="87" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20"/>
-      <c r="B3" s="21"/>
+    <row r="3" spans="1:5" ht="87" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="36"/>
+      <c r="B3" s="57"/>
       <c r="C3" s="11" t="s">
         <v>16</v>
       </c>
@@ -1628,9 +1627,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="87" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="20"/>
-      <c r="B4" s="21"/>
+    <row r="4" spans="1:5" ht="87" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="36"/>
+      <c r="B4" s="57"/>
       <c r="C4" s="12" t="s">
         <v>17</v>
       </c>
@@ -1641,87 +1640,87 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="20" t="s">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="23"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="29" t="s">
+      <c r="C5" s="45"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="51" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="20"/>
-      <c r="B6" s="22"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="30"/>
-    </row>
-    <row r="7" spans="1:5" ht="236.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="20"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="31"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="36"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="52"/>
+    </row>
+    <row r="7" spans="1:5" ht="236.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="36"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="53"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="23"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="29" t="s">
+      <c r="C8" s="45"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="51" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="20"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="30"/>
-    </row>
-    <row r="10" spans="1:5" ht="261.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="20"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="31"/>
-    </row>
-    <row r="11" spans="1:5" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="36"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="55"/>
+      <c r="E9" s="52"/>
+    </row>
+    <row r="10" spans="1:5" ht="261.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="36"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="53"/>
+    </row>
+    <row r="11" spans="1:5" ht="127.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="35" t="s">
+      <c r="D11" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="39" t="s">
+      <c r="E11" s="42" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="20"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="40"/>
-    </row>
-    <row r="13" spans="1:5" ht="134.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="20"/>
-      <c r="B13" s="22"/>
+    <row r="12" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="36"/>
+      <c r="B12" s="37"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="44"/>
+    </row>
+    <row r="13" spans="1:5" ht="134.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="36"/>
+      <c r="B13" s="37"/>
       <c r="C13" s="13" t="s">
         <v>16</v>
       </c>
@@ -1732,60 +1731,60 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="23"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="29" t="s">
+      <c r="C14" s="45"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="51" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="20"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="30"/>
-    </row>
-    <row r="16" spans="1:5" ht="288.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="20"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="31"/>
-    </row>
-    <row r="17" spans="1:5" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="20" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="36"/>
+      <c r="B15" s="37"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="52"/>
+    </row>
+    <row r="16" spans="1:5" ht="288.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="36"/>
+      <c r="B16" s="37"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="50"/>
+      <c r="E16" s="53"/>
+    </row>
+    <row r="17" spans="1:5" ht="137.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="37" t="s">
+      <c r="C17" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="35" t="s">
+      <c r="D17" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="E17" s="39" t="s">
+      <c r="E17" s="42" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="20"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="41"/>
-    </row>
-    <row r="19" spans="1:5" ht="138.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="20"/>
-      <c r="B19" s="22"/>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="36"/>
+      <c r="B18" s="37"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="43"/>
+    </row>
+    <row r="19" spans="1:5" ht="138.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="36"/>
+      <c r="B19" s="37"/>
       <c r="C19" s="13" t="s">
         <v>16</v>
       </c>
@@ -1798,21 +1797,11 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
     <mergeCell ref="D5:D7"/>
     <mergeCell ref="E5:E7"/>
     <mergeCell ref="A8:A10"/>
@@ -1820,11 +1809,21 @@
     <mergeCell ref="C8:C10"/>
     <mergeCell ref="D8:D10"/>
     <mergeCell ref="E8:E10"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Thông số kỹ thuật của Server Đông Á.xlsx
+++ b/Thông số kỹ thuật của Server Đông Á.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="50">
   <si>
     <t xml:space="preserve">Tên sản phẩm </t>
   </si>
@@ -472,6 +472,15 @@
   </si>
   <si>
     <t>T</t>
+  </si>
+  <si>
+    <t>ML</t>
+  </si>
+  <si>
+    <t>TA</t>
+  </si>
+  <si>
+    <t>MA</t>
   </si>
 </sst>
 </file>
@@ -1019,112 +1028,118 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1445,7 +1460,7 @@
   <dimension ref="C3:J6"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="9.140625" style="42"/>
+    <col min="3" max="3" width="9.140625" style="20"/>
     <col min="4" max="4" width="15.5703125" customWidth="1"/>
     <col min="5" max="5" width="14.28515625" customWidth="1"/>
     <col min="6" max="6" width="14.42578125" customWidth="1"/>
@@ -1456,64 +1471,72 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="49"/>
-      <c r="D3" s="50">
+      <c r="C3" s="21"/>
+      <c r="D3" s="22">
         <v>2</v>
       </c>
-      <c r="E3" s="50">
+      <c r="E3" s="22">
         <v>3</v>
       </c>
-      <c r="F3" s="50">
+      <c r="F3" s="22">
         <v>4</v>
       </c>
-      <c r="G3" s="50">
+      <c r="G3" s="22">
         <v>5</v>
       </c>
-      <c r="H3" s="50">
+      <c r="H3" s="22">
         <v>6</v>
       </c>
-      <c r="I3" s="50">
+      <c r="I3" s="22">
         <v>7</v>
       </c>
-      <c r="J3" s="51" t="s">
+      <c r="J3" s="23" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="4" spans="3:10" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="55" t="s">
+      <c r="C4" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="D4" s="52"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="48"/>
+      <c r="D4" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="51"/>
     </row>
     <row r="5" spans="3:10" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="56" t="s">
+      <c r="C5" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="53"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="44"/>
+      <c r="D5" s="52" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="54"/>
     </row>
     <row r="6" spans="3:10" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="57" t="s">
+      <c r="C6" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="54"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="46"/>
+      <c r="D6" s="55" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="57"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1599,10 +1622,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="87" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="48" t="s">
         <v>21</v>
       </c>
       <c r="C2" s="10" t="s">
@@ -1616,8 +1639,8 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="87" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20"/>
-      <c r="B3" s="21"/>
+      <c r="A3" s="27"/>
+      <c r="B3" s="48"/>
       <c r="C3" s="11" t="s">
         <v>16</v>
       </c>
@@ -1629,8 +1652,8 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="87" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="20"/>
-      <c r="B4" s="21"/>
+      <c r="A4" s="27"/>
+      <c r="B4" s="48"/>
       <c r="C4" s="12" t="s">
         <v>17</v>
       </c>
@@ -1642,86 +1665,86 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="23"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="29" t="s">
+      <c r="C5" s="36"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="42" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="20"/>
-      <c r="B6" s="22"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="30"/>
+      <c r="A6" s="27"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="43"/>
     </row>
     <row r="7" spans="1:5" ht="236.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="20"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="31"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="44"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="23"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="29" t="s">
+      <c r="C8" s="36"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="42" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="20"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="30"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="43"/>
     </row>
     <row r="10" spans="1:5" ht="261.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="20"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="31"/>
+      <c r="A10" s="27"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="44"/>
     </row>
     <row r="11" spans="1:5" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="35" t="s">
+      <c r="D11" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="39" t="s">
+      <c r="E11" s="33" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="20"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="40"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="35"/>
     </row>
     <row r="13" spans="1:5" ht="134.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="20"/>
-      <c r="B13" s="22"/>
+      <c r="A13" s="27"/>
+      <c r="B13" s="28"/>
       <c r="C13" s="13" t="s">
         <v>16</v>
       </c>
@@ -1733,59 +1756,59 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="23"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="29" t="s">
+      <c r="C14" s="36"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="42" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="20"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="30"/>
+      <c r="A15" s="27"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="37"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="43"/>
     </row>
     <row r="16" spans="1:5" ht="288.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="20"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="31"/>
+      <c r="A16" s="27"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="44"/>
     </row>
     <row r="17" spans="1:5" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="37" t="s">
+      <c r="C17" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="35" t="s">
+      <c r="D17" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="E17" s="39" t="s">
+      <c r="E17" s="33" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="20"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="41"/>
+      <c r="A18" s="27"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="34"/>
     </row>
     <row r="19" spans="1:5" ht="138.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="20"/>
-      <c r="B19" s="22"/>
+      <c r="A19" s="27"/>
+      <c r="B19" s="28"/>
       <c r="C19" s="13" t="s">
         <v>16</v>
       </c>
@@ -1798,21 +1821,11 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
     <mergeCell ref="D5:D7"/>
     <mergeCell ref="E5:E7"/>
     <mergeCell ref="A8:A10"/>
@@ -1820,11 +1833,21 @@
     <mergeCell ref="C8:C10"/>
     <mergeCell ref="D8:D10"/>
     <mergeCell ref="E8:E10"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
